--- a/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>VNCE</t>
   </si>
@@ -656,200 +656,213 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E7" s="2">
         <v>44954</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44590</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44226</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43862</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43498</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43134</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42763</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42399</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42035</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41671</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41307</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40936</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>292900</v>
+      </c>
+      <c r="E8" s="3">
         <v>357400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>322700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>219900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>375200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>361700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>272600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>268200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>302500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>340400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>288200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>240400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>175300</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>159600</v>
+      </c>
+      <c r="E9" s="3">
         <v>219500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>176100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>131300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>196800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>192300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>150800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>145400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>169900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>173600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>155200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>132200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>89500</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E10" s="3">
         <v>138000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>146600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>88600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>178400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>169400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>121800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>122800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>132500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>166800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>133000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>108200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>85700</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -866,8 +879,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -907,9 +921,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -949,71 +966,77 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>3600</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>26900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>20300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>55100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2700</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>16000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>700</v>
       </c>
       <c r="F15" s="3">
         <v>700</v>
       </c>
       <c r="G15" s="3">
+        <v>700</v>
+      </c>
+      <c r="H15" s="3">
         <v>1600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>600</v>
       </c>
       <c r="J15" s="3">
         <v>600</v>
@@ -1021,21 +1044,24 @@
       <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
+      <c r="L15" s="3">
+        <v>600</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="3">
-        <v>1900</v>
+      <c r="N15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O15" s="3">
         <v>1900</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1049,92 +1075,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>261300</v>
+      </c>
+      <c r="E17" s="3">
         <v>382900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>322200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>281000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>395600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>356300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>290900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>332900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>286700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>270100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>238800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>199400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132300</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-25400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-61100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-64700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>70300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>49400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>42900</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1151,92 +1184,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>50900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>76300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-18700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-69500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-81800</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-27000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-56900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>40100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>68100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-60200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>65000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>33400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-26500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-37200</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1276,93 +1316,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-63800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>30500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>58000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-68900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>59700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>30700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-38900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E24" s="3">
         <v>3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>81400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>93700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1402,93 +1451,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-38300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-65600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-23400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-162700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>35700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-29700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-41900</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-38300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-65600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>30400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-162700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>35700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-29700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-41900</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1528,9 +1586,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,30 +1610,33 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3">
         <v>82000</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-50800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-78000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-105900</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1612,9 +1676,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1654,93 +1721,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E32" s="3">
         <v>9900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-50900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-76300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>18700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>69500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>81800</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-38300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-65600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>58600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-162700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>35700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-107700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-147900</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1780,98 +1856,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-38300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-65600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>58600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-162700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>35700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-107700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-147900</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E38" s="2">
         <v>44954</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44590</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44226</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43862</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43498</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43134</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42763</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42399</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42035</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41671</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41307</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40936</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1888,8 +1973,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1906,50 +1992,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="E41" s="3">
         <v>1100</v>
       </c>
       <c r="F41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G41" s="3">
         <v>3800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1800</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1989,9 +2079,12 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1999,190 +2092,202 @@
         <v>20700</v>
       </c>
       <c r="E43" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F43" s="3">
         <v>29900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>38000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>33800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>40200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>34900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>100100</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>58800</v>
+      </c>
+      <c r="E44" s="3">
         <v>90000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>78600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>68200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>66400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>71600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>48900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>38500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>36600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>37400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>34000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>73400</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>6700</v>
       </c>
       <c r="G45" s="3">
         <v>6700</v>
       </c>
       <c r="H45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I45" s="3">
         <v>9600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>146700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>35800</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E46" s="3">
         <v>115300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>115400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>110600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>114200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>119500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>81600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>74600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>60200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>81100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>103700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>199800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>211300</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>26100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2199,93 +2304,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E48" s="3">
         <v>83100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>109800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>109700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>119900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>56700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18600</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E49" s="3">
         <v>102100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>107800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>108500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>123000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>185500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>118500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>119100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>172800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>173400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>174000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>174700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>215300</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2325,9 +2439,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2367,51 +2484,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2800</v>
       </c>
       <c r="J52" s="3">
         <v>2800</v>
       </c>
       <c r="K52" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L52" s="3">
         <v>92800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>95800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>123000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>60800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23300</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2451,51 +2574,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>225100</v>
+      </c>
+      <c r="E54" s="3">
         <v>303300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>337200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>332900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>362300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>297000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>234500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>239500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>363600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>378600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>414300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>442100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>468400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2512,8 +2641,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2530,73 +2660,77 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E57" s="3">
         <v>49400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>46700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>40200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>40300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>37000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>29100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>23800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>74500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>3500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2600</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8000</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -2607,183 +2741,198 @@
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O58" s="3">
         <v>79800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>88200</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E59" s="3">
         <v>40200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>42900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>35400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>171600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>50600</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E60" s="3">
         <v>93100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>91500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>79200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>45200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>50400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>71600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>64500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>38300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>190000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>213400</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E61" s="3">
         <v>108100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>88900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>84500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>48700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>40700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>48300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>57600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>84500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>170000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>391400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>934400</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>72600</v>
+      </c>
+      <c r="E62" s="3">
         <v>81900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>101100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>100000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>92600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>76200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>73900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>154700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>155800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>157700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>172500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>424300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>63700</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2823,9 +2972,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2865,9 +3017,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2907,51 +3062,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E66" s="3">
         <v>283100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>281400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>266700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>231500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>197800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>159800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>253500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>285100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>306700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>380800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1003400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1211500</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2968,8 +3129,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3009,9 +3171,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3051,9 +3216,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3093,9 +3261,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3135,51 +3306,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1097600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1123100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1084700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1072000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1006400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1036200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1038600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1097100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-934500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-939600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-975300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-947900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-840200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3219,9 +3396,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3261,9 +3441,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3303,51 +3486,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E76" s="3">
         <v>20300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>55800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>66200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>130800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>99200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>74800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-14000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>78500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>72000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>33600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-561300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-743000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3387,98 +3576,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45325</v>
+      </c>
+      <c r="E80" s="2">
         <v>44954</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44590</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44226</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43862</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43498</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43134</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42763</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42399</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42035</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41671</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41307</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40936</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-38300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-65600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>58600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-162700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>35700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-107700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-147900</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3495,50 +3693,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E83" s="3">
         <v>8300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3578,9 +3780,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3620,9 +3825,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3662,9 +3870,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3704,9 +3915,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3746,51 +3960,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-25100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-40400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-29700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>51600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>80300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-26000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-38300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3807,50 +4027,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1500</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3890,9 +4114,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3932,51 +4159,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E94" s="3">
         <v>1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>17500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-69600</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3993,8 +4226,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4034,9 +4268,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4076,9 +4313,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4118,9 +4358,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4160,51 +4403,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-77100</v>
+      </c>
+      <c r="E100" s="3">
         <v>17800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>31800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>28200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>58700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-27900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-81900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>56300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>8600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>104500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4223,8 +4472,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>8</v>
@@ -4238,55 +4487,61 @@
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19600</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-3400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>VNCE</t>
   </si>
@@ -783,7 +783,7 @@
         <v>219500</v>
       </c>
       <c r="F9" s="3">
-        <v>176100</v>
+        <v>168800</v>
       </c>
       <c r="G9" s="3">
         <v>131300</v>
@@ -828,7 +828,7 @@
         <v>138000</v>
       </c>
       <c r="F10" s="3">
-        <v>146600</v>
+        <v>153900</v>
       </c>
       <c r="G10" s="3">
         <v>88600</v>
@@ -976,25 +976,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-32800</v>
       </c>
       <c r="E14" s="3">
-        <v>3600</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+        <v>2000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>15800</v>
       </c>
       <c r="G14" s="3">
-        <v>26900</v>
+        <v>24600</v>
       </c>
       <c r="H14" s="3">
-        <v>20300</v>
+        <v>23900</v>
       </c>
       <c r="I14" s="3">
         <v>1700</v>
       </c>
       <c r="J14" s="3">
-        <v>5100</v>
+        <v>6100</v>
       </c>
       <c r="K14" s="3">
         <v>55100</v>
@@ -1082,25 +1082,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>261300</v>
+        <v>294100</v>
       </c>
       <c r="E17" s="3">
-        <v>382900</v>
+        <v>380900</v>
       </c>
       <c r="F17" s="3">
-        <v>322200</v>
+        <v>307200</v>
       </c>
       <c r="G17" s="3">
-        <v>281000</v>
+        <v>254100</v>
       </c>
       <c r="H17" s="3">
-        <v>395600</v>
+        <v>371700</v>
       </c>
       <c r="I17" s="3">
-        <v>356300</v>
+        <v>354600</v>
       </c>
       <c r="J17" s="3">
-        <v>290900</v>
+        <v>284800</v>
       </c>
       <c r="K17" s="3">
         <v>332900</v>
@@ -1127,25 +1127,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>31600</v>
+        <v>-1200</v>
       </c>
       <c r="E18" s="3">
-        <v>-25400</v>
+        <v>-23500</v>
       </c>
       <c r="F18" s="3">
-        <v>500</v>
+        <v>15500</v>
       </c>
       <c r="G18" s="3">
-        <v>-61100</v>
+        <v>-34200</v>
       </c>
       <c r="H18" s="3">
-        <v>-20400</v>
+        <v>3500</v>
       </c>
       <c r="I18" s="3">
-        <v>5400</v>
+        <v>7000</v>
       </c>
       <c r="J18" s="3">
-        <v>-18300</v>
+        <v>-12200</v>
       </c>
       <c r="K18" s="3">
         <v>-64700</v>
@@ -1191,25 +1191,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-11100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-8600</v>
+        <v>-1500</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G20" s="3">
-        <v>-2700</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>50900</v>
+        <v>-55800</v>
       </c>
       <c r="I20" s="3">
-        <v>-7200</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
-        <v>76300</v>
+        <v>-81900</v>
       </c>
       <c r="K20" s="3">
         <v>-4300</v>
@@ -1236,25 +1236,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>25400</v>
+        <v>400</v>
       </c>
       <c r="E21" s="3">
-        <v>-27000</v>
+        <v>-22300</v>
       </c>
       <c r="F21" s="3">
-        <v>-1600</v>
+        <v>16200</v>
       </c>
       <c r="G21" s="3">
-        <v>-56900</v>
+        <v>-33600</v>
       </c>
       <c r="H21" s="3">
-        <v>40100</v>
+        <v>60900</v>
       </c>
       <c r="I21" s="3">
-        <v>9500</v>
+        <v>9300</v>
       </c>
       <c r="J21" s="3">
-        <v>68100</v>
+        <v>70300</v>
       </c>
       <c r="K21" s="3">
         <v>-60200</v>
@@ -1281,25 +1281,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>11100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>20500</v>
+        <v>22000</v>
       </c>
       <c r="E23" s="3">
         <v>-35300</v>
@@ -1389,7 +1389,7 @@
         <v>200</v>
       </c>
       <c r="J24" s="3">
-        <v>81400</v>
+        <v>-600</v>
       </c>
       <c r="K24" s="3">
         <v>93700</v>
@@ -1461,7 +1461,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>24000</v>
+        <v>25400</v>
       </c>
       <c r="E26" s="3">
         <v>-38300</v>
@@ -1479,7 +1479,7 @@
         <v>-2000</v>
       </c>
       <c r="J26" s="3">
-        <v>-23400</v>
+        <v>58600</v>
       </c>
       <c r="K26" s="3">
         <v>-162700</v>
@@ -1509,13 +1509,13 @@
         <v>25400</v>
       </c>
       <c r="E27" s="3">
-        <v>-38300</v>
+        <v>-38400</v>
       </c>
       <c r="F27" s="3">
         <v>-12700</v>
       </c>
       <c r="G27" s="3">
-        <v>-65600</v>
+        <v>-65700</v>
       </c>
       <c r="H27" s="3">
         <v>30400</v>
@@ -1524,7 +1524,7 @@
         <v>-2000</v>
       </c>
       <c r="J27" s="3">
-        <v>-23400</v>
+        <v>58600</v>
       </c>
       <c r="K27" s="3">
         <v>-162700</v>
@@ -1595,26 +1595,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>82000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1731,25 +1731,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>11100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>9900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>8600</v>
+        <v>1500</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G32" s="3">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-50900</v>
+        <v>55800</v>
       </c>
       <c r="I32" s="3">
-        <v>7200</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
-        <v>-76300</v>
+        <v>81900</v>
       </c>
       <c r="K32" s="3">
         <v>4300</v>
@@ -2178,26 +2178,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>6700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>6700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>9600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>6500</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>4800</v>
@@ -2374,7 +2374,7 @@
         <v>123000</v>
       </c>
       <c r="I49" s="3">
-        <v>185500</v>
+        <v>144100</v>
       </c>
       <c r="J49" s="3">
         <v>118500</v>
@@ -2506,13 +2506,13 @@
         <v>4200</v>
       </c>
       <c r="H52" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="I52" s="3">
-        <v>4100</v>
+        <v>3900</v>
       </c>
       <c r="J52" s="3">
-        <v>2800</v>
+        <v>2400</v>
       </c>
       <c r="K52" s="3">
         <v>2800</v>
@@ -2712,19 +2712,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="E58" s="3">
-        <v>3500</v>
+        <v>24400</v>
       </c>
       <c r="F58" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
+        <v>25300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>22100</v>
       </c>
       <c r="H58" s="3">
-        <v>2800</v>
+        <v>23400</v>
       </c>
       <c r="I58" s="3">
         <v>20400</v>
@@ -2757,25 +2757,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>29800</v>
+        <v>1600</v>
       </c>
       <c r="E59" s="3">
-        <v>40200</v>
+        <v>1600</v>
       </c>
       <c r="F59" s="3">
-        <v>42200</v>
+        <v>1700</v>
       </c>
       <c r="G59" s="3">
-        <v>42000</v>
+        <v>1600</v>
       </c>
       <c r="H59" s="3">
-        <v>44500</v>
+        <v>1600</v>
       </c>
       <c r="I59" s="3">
-        <v>18600</v>
+        <v>1400</v>
       </c>
       <c r="J59" s="3">
-        <v>14600</v>
+        <v>1200</v>
       </c>
       <c r="K59" s="3">
         <v>13400</v>
@@ -2847,19 +2847,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>44000</v>
+        <v>111700</v>
       </c>
       <c r="E61" s="3">
-        <v>108100</v>
+        <v>180200</v>
       </c>
       <c r="F61" s="3">
-        <v>88900</v>
+        <v>183200</v>
       </c>
       <c r="G61" s="3">
-        <v>84500</v>
+        <v>181600</v>
       </c>
       <c r="H61" s="3">
-        <v>48700</v>
+        <v>138900</v>
       </c>
       <c r="I61" s="3">
         <v>42300</v>
@@ -2891,20 +2891,20 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>72600</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3">
-        <v>81900</v>
+        <v>900</v>
       </c>
       <c r="F62" s="3">
-        <v>101100</v>
+        <v>600</v>
       </c>
       <c r="G62" s="3">
-        <v>100000</v>
+        <v>1200</v>
       </c>
       <c r="H62" s="3">
-        <v>92600</v>
+        <v>2400</v>
       </c>
       <c r="I62" s="3">
         <v>76200</v>
@@ -3700,25 +3700,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="E83" s="3">
-        <v>8300</v>
+        <v>7200</v>
       </c>
       <c r="F83" s="3">
-        <v>6500</v>
+        <v>5800</v>
       </c>
       <c r="G83" s="3">
-        <v>6900</v>
+        <v>6200</v>
       </c>
       <c r="H83" s="3">
-        <v>9600</v>
+        <v>8000</v>
       </c>
       <c r="I83" s="3">
-        <v>11300</v>
+        <v>8800</v>
       </c>
       <c r="J83" s="3">
-        <v>10100</v>
+        <v>9500</v>
       </c>
       <c r="K83" s="3">
         <v>8700</v>
@@ -4463,8 +4463,8 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>VNCE</t>
   </si>
@@ -656,213 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E7" s="2">
         <v>45325</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44954</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44590</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44226</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43862</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43498</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43134</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42763</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42399</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42035</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41671</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41307</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40936</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>293500</v>
+      </c>
+      <c r="E8" s="3">
         <v>292900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>357400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>322700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>219900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>375200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>361700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>272600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>268200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>302500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>340400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>288200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>240400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>175300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>148300</v>
+      </c>
+      <c r="E9" s="3">
         <v>159600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>219500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>168800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>131300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>196800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>192300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>150800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>145400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>169900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>173600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>155200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>132200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>89500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>145200</v>
+      </c>
+      <c r="E10" s="3">
         <v>133300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>138000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>153900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>88600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>178400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>169400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>121800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>122800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>132500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>166800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>133000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>108200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>85700</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -880,8 +892,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -924,9 +937,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -969,77 +985,83 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-32800</v>
+        <v>24300</v>
       </c>
       <c r="E14" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>24600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>23900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>55100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>16800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>700</v>
       </c>
       <c r="G15" s="3">
         <v>700</v>
       </c>
       <c r="H15" s="3">
+        <v>700</v>
+      </c>
+      <c r="I15" s="3">
         <v>1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
@@ -1047,21 +1069,24 @@
       <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
+      <c r="M15" s="3">
+        <v>600</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>1900</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>1900</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1076,98 +1101,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>286300</v>
+      </c>
+      <c r="E17" s="3">
         <v>294100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>380900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>307200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>254100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>371700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>354600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>284800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>332900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>286700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>270100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>238800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>199400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>132300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-23500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-34200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-64700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>70300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>49400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>42900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1185,125 +1217,132 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-55800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-81900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-18700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-69500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-81800</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E21" s="3">
         <v>400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-22300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-33600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>60900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>70300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-60200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>16700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>65000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>33400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-26500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>11100</v>
+        <v>6600</v>
       </c>
       <c r="E22" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F22" s="3">
         <v>9900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>5000</v>
       </c>
       <c r="H22" s="3">
         <v>5000</v>
       </c>
       <c r="I22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J22" s="3">
         <v>6100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5500</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1319,99 +1358,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E23" s="3">
         <v>22000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-63800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>30500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-68900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>59700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>30700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-38900</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>93700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>24000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1454,99 +1502,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E26" s="3">
         <v>25400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-38300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-65600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>30400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>58600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-162700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>35700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>23400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-29700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-41900</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E27" s="3">
         <v>25400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-38400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-65700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>30400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>58600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-162700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-29700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-41900</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1589,9 +1646,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,27 +1676,30 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-50800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-78000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-105900</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1679,9 +1742,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1724,99 +1790,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1500</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>55800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>81900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>18700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>69500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>81800</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E33" s="3">
         <v>25400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-38300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-65600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>30400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>58600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-162700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-27400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-107700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-147900</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1859,104 +1934,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E35" s="3">
         <v>25400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-38300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-65600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>30400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>58600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-162700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-27400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-107700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-147900</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E38" s="2">
         <v>45325</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44954</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44590</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44226</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43862</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43498</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43134</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42763</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42399</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42035</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41671</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41307</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40936</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1974,8 +2058,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1993,53 +2078,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1100</v>
       </c>
       <c r="F41" s="3">
         <v>1100</v>
       </c>
       <c r="G41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H41" s="3">
         <v>3800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1800</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2082,99 +2171,108 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>20700</v>
+        <v>32900</v>
       </c>
       <c r="E43" s="3">
         <v>20700</v>
       </c>
       <c r="F43" s="3">
+        <v>20700</v>
+      </c>
+      <c r="G43" s="3">
         <v>29900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>38000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>33800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>40200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>34900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100100</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E44" s="3">
         <v>58800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>90000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>78600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>68200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>66400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>71600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>48900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>38500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>36600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>37400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>34000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>18900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>73400</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2199,80 +2297,86 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>4800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>146700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35800</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E46" s="3">
         <v>84800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>115300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>115400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>110600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>114200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>119500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>81600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>74600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>60200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>81100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>103700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>199800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>211300</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E47" s="3">
         <v>26100</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -2289,8 +2393,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2307,99 +2411,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>98600</v>
+      </c>
+      <c r="E48" s="3">
         <v>80000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>83100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>109800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>109700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>119900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>42900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>56700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18600</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>32000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>102100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>107800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>108500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>123000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>144100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>118500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>119100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>172800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>173400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>174000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>174700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>215300</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2442,9 +2555,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2487,54 +2603,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>92800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>95800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>123000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>60800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>23300</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2577,54 +2699,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>222700</v>
+      </c>
+      <c r="E54" s="3">
         <v>225100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>303300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>337200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>332900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>362300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>297000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>234500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>239500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>363600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>378600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>414300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>442100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>468400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2642,8 +2770,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2661,79 +2790,83 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E57" s="3">
         <v>31700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>49400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>46700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>40200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>43100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>40300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>37000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>28700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>23800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>74500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E58" s="3">
         <v>16800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>24400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>23400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8000</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
@@ -2744,195 +2877,210 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3">
         <v>79800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>88200</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="E59" s="3">
         <v>1600</v>
       </c>
       <c r="F59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G59" s="3">
         <v>1700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1600</v>
       </c>
       <c r="H59" s="3">
         <v>1600</v>
       </c>
       <c r="I59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>35400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>171600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>50600</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E60" s="3">
         <v>61400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>93100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>91500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>82200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>79200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>45200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>50400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>71600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>64500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>38300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>190000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>213400</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>106300</v>
+      </c>
+      <c r="E61" s="3">
         <v>111700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>180200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>183200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>181600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>138900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>42300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>48300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>57600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>84500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>170000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>391400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>934400</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>76200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>73900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>154700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>155800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>157700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>172500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>424300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>63700</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2975,9 +3123,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3020,9 +3171,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3065,54 +3219,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E66" s="3">
         <v>178000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>283100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>281400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>266700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>231500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>197800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>159800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>253500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>285100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>306700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>380800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1003400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1211500</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3130,8 +3290,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3174,9 +3335,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3219,9 +3383,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3264,9 +3431,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3309,54 +3479,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1116700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1097600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1123100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1084700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1072000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1006400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1036200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1038600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1097100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-934500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-939600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-975300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-947900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-840200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3399,9 +3575,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3444,9 +3623,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3489,54 +3671,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E76" s="3">
         <v>47200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>55800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>66200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>130800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>99200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>74800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-14000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>78500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>72000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>33600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-561300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-743000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3579,104 +3767,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E80" s="2">
         <v>45325</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44954</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44590</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44226</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43862</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43498</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43134</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42763</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42399</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42035</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41671</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41307</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40936</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E81" s="3">
         <v>25400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-38300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-65600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>30400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>58600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-162700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-27400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-107700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-147900</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3694,53 +3891,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3783,9 +3984,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3828,9 +4032,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3873,9 +4080,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3918,9 +4128,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3963,54 +4176,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E89" s="3">
         <v>1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-25100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-40400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-29700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>51600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>80300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-20700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-26000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4028,53 +4247,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4117,9 +4340,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4162,54 +4388,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E94" s="3">
         <v>75500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>17500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-69600</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4227,8 +4459,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4271,9 +4504,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4316,9 +4552,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4361,9 +4600,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4406,54 +4648,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-77100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>17800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>31800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>28200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>58700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-27900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-81900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>56300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>104500</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4463,20 +4711,20 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
@@ -4490,58 +4738,64 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>14700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19600</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VNCE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>VNCE</t>
   </si>
@@ -656,225 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45689</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45325</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44590</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44226</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43862</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43498</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43134</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42763</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42399</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42035</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41671</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41307</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40936</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300000</v>
+      </c>
+      <c r="E8" s="3">
         <v>293500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>292900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>357400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>322700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>219900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>375200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>361700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>272600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>268200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>302500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>340400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>288200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>240400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>175300</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>150900</v>
+      </c>
+      <c r="E9" s="3">
         <v>148300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>159600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>219500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>168800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>131300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>196800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>192300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>150800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>145400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>169900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>173600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>155200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>132200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>89500</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>149100</v>
+      </c>
+      <c r="E10" s="3">
         <v>145200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>133300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>138000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>153900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>88600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>178400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>169400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>121800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>122800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>132500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>166800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>133000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>108200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>85700</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -893,8 +906,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -940,9 +954,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -988,83 +1005,89 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>24300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-29700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>24600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>23900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>55100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2700</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>16000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E15" s="3">
         <v>4000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>700</v>
       </c>
       <c r="H15" s="3">
         <v>700</v>
       </c>
       <c r="I15" s="3">
+        <v>700</v>
+      </c>
+      <c r="J15" s="3">
         <v>1600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2500</v>
-      </c>
-      <c r="K15" s="3">
-        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>600</v>
@@ -1072,21 +1095,24 @@
       <c r="M15" s="3">
         <v>600</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
+      <c r="N15" s="3">
+        <v>600</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
-        <v>1900</v>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q15" s="3">
         <v>1900</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1102,104 +1128,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>290800</v>
+      </c>
+      <c r="E17" s="3">
         <v>286300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>294100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>380900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>307200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>254100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>371700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>354600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>284800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>332900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>286700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>270100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>238800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>199400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>132300</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E18" s="3">
         <v>7200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-34200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-64700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>70300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>49400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>40900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>42900</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1218,134 +1251,141 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-55800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-81900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-18700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-69500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-81800</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E21" s="3">
         <v>12200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-33600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>60900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>70300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-60200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>16700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>65000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>33400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-37200</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E22" s="3">
         <v>6600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>5000</v>
       </c>
       <c r="I22" s="3">
         <v>5000</v>
       </c>
       <c r="J22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K22" s="3">
         <v>6100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5500</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1361,105 +1401,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-63800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>30500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-68900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>59700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>30700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-38900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>93700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1505,105 +1554,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>25400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-65600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>58600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-162700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>35700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>23400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-29700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-41900</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>25400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-65700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>30400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>58600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-162700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>35700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>23400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-29700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-41900</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1649,9 +1707,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,27 +1740,30 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-50800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-105900</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1745,9 +1809,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1793,105 +1860,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>55800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>81900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>18700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>69500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>81800</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>25400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-65600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>30400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>58600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-162700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>35700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-27400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-107700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-147900</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1937,110 +2013,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>25400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-65600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>30400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>58600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-162700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>35700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-27400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-107700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-147900</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45689</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45325</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44590</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44226</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43862</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43498</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43134</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42763</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42399</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42035</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41671</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41307</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40936</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2059,8 +2144,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2079,56 +2165,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>400</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1100</v>
       </c>
       <c r="G41" s="3">
         <v>1100</v>
       </c>
       <c r="H41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I41" s="3">
         <v>3800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>21500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1800</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2174,105 +2264,114 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E43" s="3">
         <v>32900</v>
-      </c>
-      <c r="E43" s="3">
-        <v>20700</v>
       </c>
       <c r="F43" s="3">
         <v>20700</v>
       </c>
       <c r="G43" s="3">
+        <v>20700</v>
+      </c>
+      <c r="H43" s="3">
         <v>29900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>38000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>33800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>40200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>34900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100100</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E44" s="3">
         <v>59100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>58800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>90000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>78600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>68200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>66400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>71600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>48900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>38500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>36600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>37400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>34000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>18900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>73400</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2300,86 +2399,92 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>4800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>146700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>35800</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E46" s="3">
         <v>96600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>84800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>115300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>115400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>110600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>114200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>119500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>81600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>74600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>60200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>81100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>103700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>199800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>211300</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E47" s="3">
         <v>23500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>26100</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -2396,8 +2501,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2414,57 +2519,63 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E48" s="3">
         <v>98600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>80000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>83100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>109800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>109700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>119900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>56700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18600</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2472,47 +2583,50 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>32000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>102100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>107800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>108500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>123000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>144100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>118500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>119100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>172800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>173400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>174000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>174700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>215300</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2558,9 +2672,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2606,57 +2723,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E52" s="3">
         <v>4100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>92800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>95800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>123000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>60800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>23300</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2702,57 +2825,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>225000</v>
+      </c>
+      <c r="E54" s="3">
         <v>222700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>225100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>303300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>337200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>332900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>362300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>297000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>234500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>239500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>363600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>378600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>414300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>442100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>468400</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2771,8 +2900,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2791,85 +2921,89 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E57" s="3">
         <v>35100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>49400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>46700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>40200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>40300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>28700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>29100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>23800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>74500</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E58" s="3">
         <v>16000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>24400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>25300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>22100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>23400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8000</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -2880,15 +3014,18 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3">
         <v>79800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>88200</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2896,191 +3033,203 @@
         <v>1500</v>
       </c>
       <c r="E59" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F59" s="3">
         <v>1600</v>
       </c>
       <c r="G59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H59" s="3">
         <v>1700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1600</v>
       </c>
       <c r="I59" s="3">
         <v>1600</v>
       </c>
       <c r="J59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>35400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>171600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>50600</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E60" s="3">
         <v>73500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>61400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>91500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>82200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>90300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>79200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>45200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>50400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>71600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>64500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>190000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>213400</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E61" s="3">
         <v>106300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>111700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>180200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>183200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>181600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>138900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>42300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>57600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>84500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>170000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>391400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>934400</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>500</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>76200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>73900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>154700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>155800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>157700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>172500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>424300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>63700</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3126,9 +3275,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3174,9 +3326,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3222,57 +3377,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>174900</v>
+      </c>
+      <c r="E66" s="3">
         <v>181000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>178000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>283100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>281400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>266700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>231500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>197800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>159800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>253500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>285100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>306700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>380800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1003400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1211500</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3291,8 +3452,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3338,9 +3500,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3386,9 +3551,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3434,9 +3602,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3482,57 +3653,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1110300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1116700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1097600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1123100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1084700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1072000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1006400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1036200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1038600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1097100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-934500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-939600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-975300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-947900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-840200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3578,9 +3755,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3626,9 +3806,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3674,57 +3857,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E76" s="3">
         <v>41800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>55800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>66200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>130800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>99200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-14000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>78500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>72000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>33600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-561300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-743000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3770,110 +3959,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45689</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45325</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44590</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44226</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43862</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43498</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43134</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42763</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42399</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42035</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41671</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41307</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40936</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>25400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-65600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>30400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>58600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-162700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>35700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-27400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-107700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-147900</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3892,56 +4090,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E83" s="3">
         <v>4000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3987,9 +4189,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4035,9 +4240,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4083,9 +4291,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4131,9 +4342,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4179,57 +4393,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>22100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>16800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-40400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-29700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>51600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>80300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-20700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-38300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4248,56 +4468,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1500</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4343,9 +4567,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4391,57 +4618,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>75500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>17500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-69600</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4460,8 +4693,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4507,9 +4741,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4555,9 +4792,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4603,9 +4843,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4651,57 +4894,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-77100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>31800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>28200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>58700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-27900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-81900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>56300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>104500</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4714,20 +4963,20 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
@@ -4741,61 +4990,67 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>14700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19600</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-3400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
